--- a/LubanTmpl/Datas/__enums__.xlsx
+++ b/LubanTmpl/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30313"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Thirds\XIHFrameWork\LubanTmpl\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A895F07-4A07-4633-B513-5C2907D5FF5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE16892-914D-44CE-AD04-023BBE2A53D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27825" yWindow="915" windowWidth="28830" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="28830" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -102,6 +102,45 @@
   </si>
   <si>
     <t>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+  </si>
+  <si>
+    <t>ItemEnum</t>
+  </si>
+  <si>
+    <t>Coin</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>Game1Prop1</t>
+  </si>
+  <si>
+    <t>道具1</t>
+  </si>
+  <si>
+    <t>Game1Prop2</t>
+  </si>
+  <si>
+    <t>道具2</t>
+  </si>
+  <si>
+    <t>Game1Prop3</t>
+  </si>
+  <si>
+    <t>道具3</t>
+  </si>
+  <si>
+    <t>Game1Revive1</t>
+  </si>
+  <si>
+    <t>复活方式1</t>
   </si>
 </sst>
 </file>
@@ -154,7 +193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -163,6 +202,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -565,6 +610,110 @@
         <v>24</v>
       </c>
     </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2001</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
